--- a/data_lake/behavior/NAAIM Exposure Index.xlsx
+++ b/data_lake/behavior/NAAIM Exposure Index.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\behavior\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\behavior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1AAA831-9003-43C9-B37E-354AB9D656C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8F81A3-8EF2-4C1F-96E8-13CF06E0DBE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAAIM" sheetId="1" r:id="rId1"/>
@@ -3986,6 +3986,9 @@
                 <c:pt idx="1043">
                   <c:v>46198</c:v>
                 </c:pt>
+                <c:pt idx="1044">
+                  <c:v>46205</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7126,6 +7129,9 @@
                 </c:pt>
                 <c:pt idx="1043">
                   <c:v>98.59</c:v>
+                </c:pt>
+                <c:pt idx="1044">
+                  <c:v>84.69</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10542,6 +10548,9 @@
                 <c:pt idx="1043">
                   <c:v>46198</c:v>
                 </c:pt>
+                <c:pt idx="1044">
+                  <c:v>46205</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13682,6 +13691,9 @@
                 </c:pt>
                 <c:pt idx="1043">
                   <c:v>43.91</c:v>
+                </c:pt>
+                <c:pt idx="1044">
+                  <c:v>54.64</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15388,7 +15400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1045"/>
+  <dimension ref="A1:L1046"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="8" bestFit="1" customWidth="1"/>
@@ -56750,7 +56762,7 @@
         <v>47.62</v>
       </c>
       <c r="L1027" s="19">
-        <f t="shared" ref="L1027:L1045" si="33">IF(OR(K1027=0,I1027=G1027,J1027=F1027),"",0.4*((3*(E1027-H1027)/K1027)/(1+ABS(3*(E1027-H1027)/K1027)))+0.45*((I1027+G1027-2*H1027)/(I1027-G1027))+0.15*((J1027+F1027-2*H1027)/(J1027-F1027)))</f>
+        <f t="shared" ref="L1027:L1046" si="33">IF(OR(K1027=0,I1027=G1027,J1027=F1027),"",0.4*((3*(E1027-H1027)/K1027)/(1+ABS(3*(E1027-H1027)/K1027)))+0.45*((I1027+G1027-2*H1027)/(I1027-G1027))+0.15*((J1027+F1027-2*H1027)/(J1027-F1027)))</f>
         <v>-0.56220481668637778</v>
       </c>
     </row>
@@ -57520,7 +57532,7 @@
         <v>0.41666666666674601</v>
       </c>
       <c r="D1045" s="8" t="str">
-        <f t="shared" ref="D1045" si="39">IF(
+        <f t="shared" ref="D1045:D1046" si="39">IF(
  AND(
   B1045 &gt;= IF(
          YEAR(B1045)&gt;=2007,
@@ -57562,6 +57574,46 @@
       <c r="L1045" s="19">
         <f t="shared" si="33"/>
         <v>-0.397178806845285</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:12">
+      <c r="A1046" s="8">
+        <v>46204</v>
+      </c>
+      <c r="B1046" s="8">
+        <v>46205</v>
+      </c>
+      <c r="C1046" s="9">
+        <v>0.41666666666675201</v>
+      </c>
+      <c r="D1046" s="8" t="str">
+        <f t="shared" si="39"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E1046" s="10">
+        <v>84.69</v>
+      </c>
+      <c r="F1046" s="11">
+        <v>0</v>
+      </c>
+      <c r="G1046" s="10">
+        <v>63.75</v>
+      </c>
+      <c r="H1046" s="12">
+        <v>96.5</v>
+      </c>
+      <c r="I1046" s="12">
+        <v>100</v>
+      </c>
+      <c r="J1046" s="12">
+        <v>200</v>
+      </c>
+      <c r="K1046" s="10">
+        <v>54.64</v>
+      </c>
+      <c r="L1046" s="19">
+        <f t="shared" si="33"/>
+        <v>-0.51519773605203623</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/behavior/NAAIM Exposure Index.xlsx
+++ b/data_lake/behavior/NAAIM Exposure Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data_lake\behavior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C045EA7A-C127-4071-8DD1-2BCEE4087995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE30D61C-8777-47C5-8E7C-C4A8828342FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAAIM" sheetId="1" r:id="rId1"/>
@@ -4017,6 +4017,9 @@
                 <c:pt idx="1045">
                   <c:v>46212</c:v>
                 </c:pt>
+                <c:pt idx="1046">
+                  <c:v>46219</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7163,6 +7166,9 @@
                 </c:pt>
                 <c:pt idx="1045">
                   <c:v>82.95</c:v>
+                </c:pt>
+                <c:pt idx="1046">
+                  <c:v>95.64</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10585,6 +10591,9 @@
                 <c:pt idx="1045">
                   <c:v>46212</c:v>
                 </c:pt>
+                <c:pt idx="1046">
+                  <c:v>46219</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13731,6 +13740,9 @@
                 </c:pt>
                 <c:pt idx="1045">
                   <c:v>58.71</c:v>
+                </c:pt>
+                <c:pt idx="1046">
+                  <c:v>47.97</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15437,7 +15449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1047"/>
+  <dimension ref="A1:L1048"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="10.08984375" style="17" bestFit="1" customWidth="1"/>
@@ -56799,7 +56811,7 @@
         <v>47.62</v>
       </c>
       <c r="L1027" s="22">
-        <f t="shared" ref="L1027:L1047" si="33">IF(OR(K1027=0,I1027=G1027,J1027=F1027),"",0.4*((3*(E1027-H1027)/K1027)/(1+ABS(3*(E1027-H1027)/K1027)))+0.45*((I1027+G1027-2*H1027)/(I1027-G1027))+0.15*((J1027+F1027-2*H1027)/(J1027-F1027)))</f>
+        <f t="shared" ref="L1027:L1048" si="33">IF(OR(K1027=0,I1027=G1027,J1027=F1027),"",0.4*((3*(E1027-H1027)/K1027)/(1+ABS(3*(E1027-H1027)/K1027)))+0.45*((I1027+G1027-2*H1027)/(I1027-G1027))+0.15*((J1027+F1027-2*H1027)/(J1027-F1027)))</f>
         <v>-0.56220481668637778</v>
       </c>
     </row>
@@ -57691,6 +57703,61 @@
       <c r="L1047" s="22">
         <f t="shared" si="33"/>
         <v>-0.59610331066968847</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:12">
+      <c r="A1048" s="17">
+        <v>46218</v>
+      </c>
+      <c r="B1048" s="17">
+        <v>46219</v>
+      </c>
+      <c r="C1048" s="18">
+        <v>0.416666666666764</v>
+      </c>
+      <c r="D1048" s="17" t="str">
+        <f t="shared" ref="D1048" si="40">IF(
+ AND(
+  B1048 &gt;= IF(
+         YEAR(B1048)&gt;=2007,
+         DATE(YEAR(B1048),3,14)-WEEKDAY(DATE(YEAR(B1048),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B1048),4,7)-WEEKDAY(DATE(YEAR(B1048),4,7),1)+1 + TIME(2,0,0)
+       ),
+  B1048 &lt;  IF(
+         YEAR(B1048)&gt;=2007,
+         DATE(YEAR(B1048),11,7)-WEEKDAY(DATE(YEAR(B1048),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B1048),10,31)-WEEKDAY(DATE(YEAR(B1048),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
+      </c>
+      <c r="E1048" s="19">
+        <v>95.64</v>
+      </c>
+      <c r="F1048" s="20">
+        <v>-25</v>
+      </c>
+      <c r="G1048" s="19">
+        <v>90</v>
+      </c>
+      <c r="H1048" s="21">
+        <v>100</v>
+      </c>
+      <c r="I1048" s="21">
+        <v>100</v>
+      </c>
+      <c r="J1048" s="21">
+        <v>200</v>
+      </c>
+      <c r="K1048" s="19">
+        <v>47.97</v>
+      </c>
+      <c r="L1048" s="22">
+        <f t="shared" si="33"/>
+        <v>-0.55236691236691249</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/behavior/NAAIM Exposure Index.xlsx
+++ b/data_lake/behavior/NAAIM Exposure Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\behavior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91122423-0294-4223-9DB0-46703245D9F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E1A799-7740-4691-A757-03BDEB3CBBC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -696,7 +696,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="43"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -745,6 +745,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="45">
     <cellStyle name="20% - 강조색1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -4007,6 +4008,9 @@
                 <c:pt idx="1045">
                   <c:v>46226</c:v>
                 </c:pt>
+                <c:pt idx="1046">
+                  <c:v>46233</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7153,6 +7157,9 @@
                 </c:pt>
                 <c:pt idx="1045">
                   <c:v>84.02</c:v>
+                </c:pt>
+                <c:pt idx="1046">
+                  <c:v>79.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10577,6 +10584,9 @@
                 <c:pt idx="1045">
                   <c:v>46226</c:v>
                 </c:pt>
+                <c:pt idx="1046">
+                  <c:v>46233</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13723,6 +13733,9 @@
                 </c:pt>
                 <c:pt idx="1045">
                   <c:v>43.61</c:v>
+                </c:pt>
+                <c:pt idx="1046">
+                  <c:v>48.99</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -22584,7 +22597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1047"/>
+  <dimension ref="A1:L1048"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.19921875" style="7" bestFit="1" customWidth="1"/>
@@ -63851,7 +63864,7 @@
         <v>47.62</v>
       </c>
       <c r="L1025" s="12">
-        <f t="shared" ref="L1025:L1047" si="33">IF(OR(K1025=0,I1025=G1025,J1025=F1025),"",0.4*((3*(E1025-H1025)/K1025)/(1+ABS(3*(E1025-H1025)/K1025)))+0.45*((I1025+G1025-2*H1025)/(I1025-G1025))+0.15*((J1025+F1025-2*H1025)/(J1025-F1025)))</f>
+        <f t="shared" ref="L1025:L1048" si="33">IF(OR(K1025=0,I1025=G1025,J1025=F1025),"",0.4*((3*(E1025-H1025)/K1025)/(1+ABS(3*(E1025-H1025)/K1025)))+0.45*((I1025+G1025-2*H1025)/(I1025-G1025))+0.15*((J1025+F1025-2*H1025)/(J1025-F1025)))</f>
         <v>-0.56220481668637778</v>
       </c>
     </row>
@@ -64756,7 +64769,7 @@
         <v>0.416666666666764</v>
       </c>
       <c r="D1046" s="7" t="str">
-        <f t="shared" ref="D1046:D1047" si="40">IF(
+        <f t="shared" ref="D1046:D1048" si="40">IF(
  AND(
   B1046 &gt;= IF(
          YEAR(B1046)&gt;=2007,
@@ -64838,6 +64851,46 @@
       <c r="L1047" s="12">
         <f t="shared" si="33"/>
         <v>-0.36716890881913306</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1048" s="7">
+        <v>46232</v>
+      </c>
+      <c r="B1048" s="7">
+        <v>46233</v>
+      </c>
+      <c r="C1048" s="8">
+        <v>0.41666666666677599</v>
+      </c>
+      <c r="D1048" s="7" t="str">
+        <f t="shared" si="40"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E1048" s="9">
+        <v>79.7</v>
+      </c>
+      <c r="F1048" s="10">
+        <v>0</v>
+      </c>
+      <c r="G1048" s="9">
+        <v>60</v>
+      </c>
+      <c r="H1048" s="11">
+        <v>90</v>
+      </c>
+      <c r="I1048" s="11">
+        <v>100</v>
+      </c>
+      <c r="J1048" s="11">
+        <v>200</v>
+      </c>
+      <c r="K1048" s="9">
+        <v>48.99</v>
+      </c>
+      <c r="L1048" s="12">
+        <f t="shared" si="33"/>
+        <v>-0.36471273000375515</v>
       </c>
     </row>
   </sheetData>
@@ -65109,6 +65162,33 @@
       <c r="D6" s="7" t="str">
         <f t="shared" si="3"/>
         <v>UTC-4</v>
+      </c>
+      <c r="E6" s="20">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="F6" s="20">
+        <v>0.44700000000000001</v>
+      </c>
+      <c r="G6" s="20">
+        <v>0.16070000000000001</v>
+      </c>
+      <c r="H6" s="20">
+        <v>0.17860000000000001</v>
+      </c>
+      <c r="I6" s="20">
+        <v>0.03</v>
+      </c>
+      <c r="J6" s="20">
+        <v>3.3300000000000003E-2</v>
+      </c>
+      <c r="K6" s="20">
+        <v>0.15</v>
+      </c>
+      <c r="L6" s="22">
+        <v>-7.9000000000000001E-2</v>
+      </c>
+      <c r="M6" s="22">
+        <v>0.11849999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/behavior/NAAIM Exposure Index.xlsx
+++ b/data_lake/behavior/NAAIM Exposure Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\behavior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FB99DB2-5E3B-4EAA-8C7F-81074591703A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D6A02E-9B3C-4B3F-907D-2F068291D9D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAAIM" sheetId="1" r:id="rId1"/>
@@ -707,7 +707,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="177" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -754,7 +754,6 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="43" applyFont="1"/>
   </cellXfs>
@@ -4021,6 +4020,9 @@
                 </c:pt>
                 <c:pt idx="1046">
                   <c:v>46233</c:v>
+                </c:pt>
+                <c:pt idx="1047">
+                  <c:v>46240</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10597,6 +10599,9 @@
                 </c:pt>
                 <c:pt idx="1046">
                   <c:v>46233</c:v>
+                </c:pt>
+                <c:pt idx="1047">
+                  <c:v>46240</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -22608,7 +22613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1048"/>
+  <dimension ref="A1:L1049"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.19921875" style="5" bestFit="1" customWidth="1"/>
@@ -64904,6 +64909,36 @@
         <v>-0.36471273000375515</v>
       </c>
     </row>
+    <row r="1049" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1049" s="5">
+        <v>46239</v>
+      </c>
+      <c r="B1049" s="5">
+        <v>46240</v>
+      </c>
+      <c r="C1049" s="6">
+        <v>0.41666666666678198</v>
+      </c>
+      <c r="D1049" s="5" t="str">
+        <f t="shared" ref="D1049" si="41">IF(
+ AND(
+  B1049 &gt;= IF(
+         YEAR(B1049)&gt;=2007,
+         DATE(YEAR(B1049),3,14)-WEEKDAY(DATE(YEAR(B1049),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B1049),4,7)-WEEKDAY(DATE(YEAR(B1049),4,7),1)+1 + TIME(2,0,0)
+       ),
+  B1049 &lt;  IF(
+         YEAR(B1049)&gt;=2007,
+         DATE(YEAR(B1049),11,7)-WEEKDAY(DATE(YEAR(B1049),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B1049),10,31)-WEEKDAY(DATE(YEAR(B1049),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -64913,7 +64948,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9EBD50E-72EC-42F7-90EF-D55F0BDD9D7D}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.296875" style="5" bestFit="1" customWidth="1"/>
@@ -64921,8 +64956,9 @@
     <col min="3" max="3" width="11.296875" style="19" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="19" bestFit="1" customWidth="1"/>
     <col min="5" max="11" width="8.796875" style="18"/>
-    <col min="12" max="12" width="9.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.796875" style="12"/>
+    <col min="12" max="12" width="9.5" style="18" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.796875" style="18"/>
+    <col min="14" max="16384" width="8.796875" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
@@ -65025,7 +65061,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
-        <f t="shared" ref="A3:B5" si="1">A2+7</f>
+        <f t="shared" ref="A3:B7" si="1">A2+7</f>
         <v>46205</v>
       </c>
       <c r="B3" s="5">
@@ -65112,7 +65148,7 @@
         <v>0.41666666666674601</v>
       </c>
       <c r="D5" s="5" t="str">
-        <f t="shared" ref="D5:D6" si="3">IF(
+        <f t="shared" ref="D5:D7" si="3">IF(
  AND(
   B5 &gt;= IF(
          YEAR(B5)&gt;=2007,
@@ -65195,11 +65231,55 @@
       <c r="K6" s="18">
         <v>0.15</v>
       </c>
-      <c r="L6" s="20">
+      <c r="L6" s="18">
         <v>-7.9000000000000001E-2</v>
       </c>
-      <c r="M6" s="20">
+      <c r="M6" s="18">
         <v>0.11849999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <f t="shared" si="1"/>
+        <v>46233</v>
+      </c>
+      <c r="B7" s="5">
+        <f t="shared" si="1"/>
+        <v>46237</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.41666666666674601</v>
+      </c>
+      <c r="D7" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E7" s="18">
+        <v>0.60699999999999998</v>
+      </c>
+      <c r="F7" s="18">
+        <v>0.39300000000000002</v>
+      </c>
+      <c r="G7" s="18">
+        <v>0.19639999999999999</v>
+      </c>
+      <c r="H7" s="18">
+        <v>0.16070000000000001</v>
+      </c>
+      <c r="I7" s="18">
+        <v>0.05</v>
+      </c>
+      <c r="J7" s="18">
+        <v>0.05</v>
+      </c>
+      <c r="K7" s="18">
+        <v>0.15</v>
+      </c>
+      <c r="L7" s="18">
+        <v>1.1900000000000001E-2</v>
+      </c>
+      <c r="M7" s="18">
+        <v>-1.7899999999999999E-2</v>
       </c>
     </row>
   </sheetData>
@@ -65228,13 +65308,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="21" t="s">
         <v>8</v>
       </c>
     </row>
@@ -65258,7 +65338,7 @@
       <c r="C5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="21" t="s">
         <v>16</v>
       </c>
     </row>
@@ -65295,7 +65375,7 @@
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="21" t="s">
         <v>40</v>
       </c>
     </row>

--- a/data_lake/behavior/NAAIM Exposure Index.xlsx
+++ b/data_lake/behavior/NAAIM Exposure Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\behavior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D6A02E-9B3C-4B3F-907D-2F068291D9D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA804078-D9F1-4BFC-927A-152A8F81A04F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -98,9 +98,6 @@
     <t>https://ycharts.com/indicators/naaim_survey_of_managers_2nd_quartile</t>
   </si>
   <si>
-    <t>https://ycharts.com/indicators/naaim_number</t>
-  </si>
-  <si>
     <t>https://ycharts.com/indicators/naaim_survey_of_managers_deviation</t>
   </si>
   <si>
@@ -162,6 +159,10 @@
   </si>
   <si>
     <t>https://www.ceicdata.com/en/united-states/naaim-exposure-index</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ycharts.com/indicators/naaim_number</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -707,7 +708,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="177" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -756,6 +757,7 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="43" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="43"/>
   </cellXfs>
   <cellStyles count="45">
     <cellStyle name="20% - 강조색1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -22645,28 +22647,28 @@
         <v>7</v>
       </c>
       <c r="E1" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="G1" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="H1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="I1" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="J1" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="K1" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="L1" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -64975,31 +64977,31 @@
         <v>7</v>
       </c>
       <c r="E1" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="G1" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="H1" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="I1" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="J1" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="K1" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="L1" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="M1" s="17" t="s">
         <v>30</v>
-      </c>
-      <c r="M1" s="17" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -65318,12 +65320,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="C3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="12" t="s">
-        <v>19</v>
+      <c r="D3" s="22" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.3">
@@ -65331,7 +65333,7 @@
         <v>13</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.3">
@@ -65363,7 +65365,7 @@
         <v>14</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.3">
@@ -65371,12 +65373,12 @@
         <v>15</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.3">
       <c r="D10" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.3">
@@ -65393,6 +65395,7 @@
     <hyperlink ref="D2" r:id="rId1" xr:uid="{A82A1AB3-CBB7-F444-B7E1-7D406688AF01}"/>
     <hyperlink ref="D5" r:id="rId2" xr:uid="{113F6732-0185-4C2B-AA6C-637F02D708EB}"/>
     <hyperlink ref="D10" r:id="rId3" xr:uid="{D5D2537C-B081-444E-9E53-E5963D21C9AF}"/>
+    <hyperlink ref="D3" r:id="rId4" xr:uid="{334F31D1-5BA7-4173-A87E-E83A189D7B7E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_lake/behavior/NAAIM Exposure Index.xlsx
+++ b/data_lake/behavior/NAAIM Exposure Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\behavior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA804078-D9F1-4BFC-927A-152A8F81A04F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9202B187-49B0-4C35-A722-0BFC8663FA4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAAIM" sheetId="1" r:id="rId1"/>
@@ -64950,7 +64950,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9EBD50E-72EC-42F7-90EF-D55F0BDD9D7D}">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.296875" style="5" bestFit="1" customWidth="1"/>
@@ -65198,11 +65198,11 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
-        <f t="shared" ref="A6" si="4">A5+7</f>
+        <f t="shared" ref="A6:A8" si="4">A5+7</f>
         <v>46226</v>
       </c>
       <c r="B6" s="5">
-        <f t="shared" ref="B6" si="5">B5+7</f>
+        <f t="shared" ref="B6:B8" si="5">B5+7</f>
         <v>46230</v>
       </c>
       <c r="C6" s="6">
@@ -65282,6 +65282,65 @@
       </c>
       <c r="M7" s="18">
         <v>-1.7899999999999999E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <f t="shared" si="4"/>
+        <v>46240</v>
+      </c>
+      <c r="B8" s="5">
+        <f t="shared" si="5"/>
+        <v>46244</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.41666666666674601</v>
+      </c>
+      <c r="D8" s="5" t="str">
+        <f t="shared" ref="D8" si="6">IF(
+ AND(
+  B8 &gt;= IF(
+         YEAR(B8)&gt;=2007,
+         DATE(YEAR(B8),3,14)-WEEKDAY(DATE(YEAR(B8),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B8),4,7)-WEEKDAY(DATE(YEAR(B8),4,7),1)+1 + TIME(2,0,0)
+       ),
+  B8 &lt;  IF(
+         YEAR(B8)&gt;=2007,
+         DATE(YEAR(B8),11,7)-WEEKDAY(DATE(YEAR(B8),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B8),10,31)-WEEKDAY(DATE(YEAR(B8),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
+      </c>
+      <c r="E8" s="18">
+        <v>0.65300000000000002</v>
+      </c>
+      <c r="F8" s="18">
+        <v>0.34699999999999998</v>
+      </c>
+      <c r="G8" s="18">
+        <v>0.25</v>
+      </c>
+      <c r="H8" s="18">
+        <v>0.19639999999999999</v>
+      </c>
+      <c r="I8" s="18">
+        <v>0.04</v>
+      </c>
+      <c r="J8" s="18">
+        <v>1.67E-2</v>
+      </c>
+      <c r="K8" s="18">
+        <v>0.15</v>
+      </c>
+      <c r="L8" s="18">
+        <v>8.8499999999999995E-2</v>
+      </c>
+      <c r="M8" s="18">
+        <v>-0.13270000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/behavior/NAAIM Exposure Index.xlsx
+++ b/data_lake/behavior/NAAIM Exposure Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\behavior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9202B187-49B0-4C35-A722-0BFC8663FA4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDCDB8A0-579B-4065-8DF3-F202DF6E5B05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAAIM" sheetId="1" r:id="rId1"/>
@@ -4026,6 +4026,9 @@
                 <c:pt idx="1047">
                   <c:v>46240</c:v>
                 </c:pt>
+                <c:pt idx="1048">
+                  <c:v>46247</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10604,6 +10607,9 @@
                 </c:pt>
                 <c:pt idx="1047">
                   <c:v>46240</c:v>
+                </c:pt>
+                <c:pt idx="1048">
+                  <c:v>46247</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -22615,7 +22621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1049"/>
+  <dimension ref="A1:L1050"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.19921875" style="5" bestFit="1" customWidth="1"/>
@@ -64922,7 +64928,7 @@
         <v>0.41666666666678198</v>
       </c>
       <c r="D1049" s="5" t="str">
-        <f t="shared" ref="D1049" si="41">IF(
+        <f t="shared" ref="D1049:D1050" si="41">IF(
  AND(
   B1049 &gt;= IF(
          YEAR(B1049)&gt;=2007,
@@ -64938,6 +64944,21 @@
  "UTC-4",
  "UTC-5"
 )</f>
+        <v>UTC-4</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1050" s="5">
+        <v>46246</v>
+      </c>
+      <c r="B1050" s="5">
+        <v>46247</v>
+      </c>
+      <c r="C1050" s="6">
+        <v>0.41666666666678798</v>
+      </c>
+      <c r="D1050" s="5" t="str">
+        <f t="shared" si="41"/>
         <v>UTC-4</v>
       </c>
     </row>

--- a/data_lake/behavior/NAAIM Exposure Index.xlsx
+++ b/data_lake/behavior/NAAIM Exposure Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\behavior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDCDB8A0-579B-4065-8DF3-F202DF6E5B05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{427FE329-30BE-4717-9053-9DA26749B080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7178,6 +7178,9 @@
                 </c:pt>
                 <c:pt idx="1046">
                   <c:v>79.7</c:v>
+                </c:pt>
+                <c:pt idx="1047">
+                  <c:v>95</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -64946,6 +64949,9 @@
 )</f>
         <v>UTC-4</v>
       </c>
+      <c r="E1049" s="7">
+        <v>95</v>
+      </c>
     </row>
     <row r="1050" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1050" s="5">

--- a/data_lake/behavior/NAAIM Exposure Index.xlsx
+++ b/data_lake/behavior/NAAIM Exposure Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\behavior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{427FE329-30BE-4717-9053-9DA26749B080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9E8957-9C0E-4648-B73A-32C7AE11D0B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAAIM" sheetId="1" r:id="rId1"/>
@@ -64977,7 +64977,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9EBD50E-72EC-42F7-90EF-D55F0BDD9D7D}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.296875" style="5" bestFit="1" customWidth="1"/>
@@ -65225,11 +65225,11 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
-        <f t="shared" ref="A6:A8" si="4">A5+7</f>
+        <f t="shared" ref="A6:A9" si="4">A5+7</f>
         <v>46226</v>
       </c>
       <c r="B6" s="5">
-        <f t="shared" ref="B6:B8" si="5">B5+7</f>
+        <f t="shared" ref="B6:B9" si="5">B5+7</f>
         <v>46230</v>
       </c>
       <c r="C6" s="6">
@@ -65324,7 +65324,7 @@
         <v>0.41666666666674601</v>
       </c>
       <c r="D8" s="5" t="str">
-        <f t="shared" ref="D8" si="6">IF(
+        <f t="shared" ref="D8:D9" si="6">IF(
  AND(
   B8 &gt;= IF(
          YEAR(B8)&gt;=2007,
@@ -65368,6 +65368,50 @@
       </c>
       <c r="M8" s="18">
         <v>-0.13270000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <f t="shared" si="4"/>
+        <v>46247</v>
+      </c>
+      <c r="B9" s="5">
+        <f t="shared" si="5"/>
+        <v>46251</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.41666666666674601</v>
+      </c>
+      <c r="D9" s="5" t="str">
+        <f t="shared" si="6"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E9" s="18">
+        <v>0.59099999999999997</v>
+      </c>
+      <c r="F9" s="18">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="G9" s="18">
+        <v>0.21429999999999999</v>
+      </c>
+      <c r="H9" s="18">
+        <v>0.19639999999999999</v>
+      </c>
+      <c r="I9" s="18">
+        <v>0.03</v>
+      </c>
+      <c r="J9" s="18">
+        <v>0</v>
+      </c>
+      <c r="K9" s="18">
+        <v>0.15</v>
+      </c>
+      <c r="L9" s="18">
+        <v>-1.55E-2</v>
+      </c>
+      <c r="M9" s="18">
+        <v>2.3199999999999998E-2</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/behavior/NAAIM Exposure Index.xlsx
+++ b/data_lake/behavior/NAAIM Exposure Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\behavior\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9E8957-9C0E-4648-B73A-32C7AE11D0B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E866E2-9562-4A9E-8D70-4E88AD54B730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAAIM" sheetId="1" r:id="rId1"/>
@@ -4029,6 +4029,9 @@
                 <c:pt idx="1048">
                   <c:v>46247</c:v>
                 </c:pt>
+                <c:pt idx="1049">
+                  <c:v>46254</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -10613,6 +10616,9 @@
                 </c:pt>
                 <c:pt idx="1048">
                   <c:v>46247</c:v>
+                </c:pt>
+                <c:pt idx="1049">
+                  <c:v>46254</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -22624,7 +22630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1050"/>
+  <dimension ref="A1:L1051"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.19921875" style="5" bestFit="1" customWidth="1"/>
@@ -64931,7 +64937,7 @@
         <v>0.41666666666678198</v>
       </c>
       <c r="D1049" s="5" t="str">
-        <f t="shared" ref="D1049:D1050" si="41">IF(
+        <f t="shared" ref="D1049:D1051" si="41">IF(
  AND(
   B1049 &gt;= IF(
          YEAR(B1049)&gt;=2007,
@@ -64964,6 +64970,21 @@
         <v>0.41666666666678798</v>
       </c>
       <c r="D1050" s="5" t="str">
+        <f t="shared" si="41"/>
+        <v>UTC-4</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1051" s="5">
+        <v>46253</v>
+      </c>
+      <c r="B1051" s="5">
+        <v>46254</v>
+      </c>
+      <c r="C1051" s="6">
+        <v>0.41666666666679397</v>
+      </c>
+      <c r="D1051" s="5" t="str">
         <f t="shared" si="41"/>
         <v>UTC-4</v>
       </c>

--- a/data_lake/behavior/NAAIM Exposure Index.xlsx
+++ b/data_lake/behavior/NAAIM Exposure Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/behavior/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E7238D-2723-2349-B0FE-2CA92D67C928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{551DD60A-31C5-EF42-9582-1127746CB9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15020" yWindow="780" windowWidth="20980" windowHeight="20700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15020" yWindow="780" windowWidth="20980" windowHeight="20700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAAIM" sheetId="1" r:id="rId1"/>
@@ -7186,7 +7186,16 @@
                   <c:v>79.7</c:v>
                 </c:pt>
                 <c:pt idx="1047">
-                  <c:v>95</c:v>
+                  <c:v>82.5</c:v>
+                </c:pt>
+                <c:pt idx="1048">
+                  <c:v>95.5</c:v>
+                </c:pt>
+                <c:pt idx="1049">
+                  <c:v>94</c:v>
+                </c:pt>
+                <c:pt idx="1050">
+                  <c:v>102.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -64962,7 +64971,7 @@
         <v>UTC-4</v>
       </c>
       <c r="E1049" s="7">
-        <v>95</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="1050" spans="1:12" x14ac:dyDescent="0.2">
@@ -64979,6 +64988,9 @@
         <f t="shared" si="41"/>
         <v>UTC-4</v>
       </c>
+      <c r="E1050" s="7">
+        <v>95.5</v>
+      </c>
     </row>
     <row r="1051" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1051" s="5">
@@ -64993,6 +65005,9 @@
       <c r="D1051" s="5" t="str">
         <f t="shared" si="41"/>
         <v>UTC-4</v>
+      </c>
+      <c r="E1051" s="7">
+        <v>94</v>
       </c>
     </row>
     <row r="1052" spans="1:12" x14ac:dyDescent="0.2">
@@ -65023,6 +65038,9 @@
  "UTC-5"
 )</f>
         <v>UTC-4</v>
+      </c>
+      <c r="E1052" s="7">
+        <v>102.7</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/behavior/NAAIM Exposure Index.xlsx
+++ b/data_lake/behavior/NAAIM Exposure Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/behavior/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{551DD60A-31C5-EF42-9582-1127746CB9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91626206-E925-7741-A753-959BC23783D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15020" yWindow="780" windowWidth="20980" windowHeight="20700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15020" yWindow="780" windowWidth="20980" windowHeight="20700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAAIM" sheetId="1" r:id="rId1"/>
@@ -4035,6 +4035,9 @@
                 <c:pt idx="1050">
                   <c:v>46261</c:v>
                 </c:pt>
+                <c:pt idx="1051">
+                  <c:v>46268</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7195,7 +7198,10 @@
                   <c:v>94</c:v>
                 </c:pt>
                 <c:pt idx="1050">
-                  <c:v>102.7</c:v>
+                  <c:v>102.66</c:v>
+                </c:pt>
+                <c:pt idx="1051">
+                  <c:v>85.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10634,6 +10640,9 @@
                 </c:pt>
                 <c:pt idx="1050">
                   <c:v>46261</c:v>
+                </c:pt>
+                <c:pt idx="1051">
+                  <c:v>46268</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -22645,7 +22654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1052"/>
+  <dimension ref="A1:L1053"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="5" bestFit="1" customWidth="1"/>
@@ -65021,7 +65030,7 @@
         <v>0.41666666666680002</v>
       </c>
       <c r="D1052" s="5" t="str">
-        <f t="shared" ref="D1052" si="42">IF(
+        <f t="shared" ref="D1052:D1053" si="42">IF(
  AND(
   B1052 &gt;= IF(
          YEAR(B1052)&gt;=2007,
@@ -65040,7 +65049,25 @@
         <v>UTC-4</v>
       </c>
       <c r="E1052" s="7">
-        <v>102.7</v>
+        <v>102.66</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1053" s="5">
+        <v>46267</v>
+      </c>
+      <c r="B1053" s="5">
+        <v>46268</v>
+      </c>
+      <c r="C1053" s="6">
+        <v>0.41666666666680602</v>
+      </c>
+      <c r="D1053" s="5" t="str">
+        <f t="shared" si="42"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E1053" s="7">
+        <v>85.6</v>
       </c>
     </row>
   </sheetData>
@@ -65052,7 +65079,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9EBD50E-72EC-42F7-90EF-D55F0BDD9D7D}">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -65300,11 +65327,11 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
-        <f t="shared" ref="A6:B10" si="4">A5+7</f>
+        <f t="shared" ref="A6:B11" si="4">A5+7</f>
         <v>46226</v>
       </c>
       <c r="B6" s="5">
-        <f t="shared" ref="B6:B9" si="5">B5+7</f>
+        <f t="shared" ref="B6:B11" si="5">B5+7</f>
         <v>46230</v>
       </c>
       <c r="C6" s="6">
@@ -65531,6 +65558,38 @@
       </c>
       <c r="M10" s="18">
         <v>0.20480000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11" s="5">
+        <f t="shared" si="4"/>
+        <v>46261</v>
+      </c>
+      <c r="B11" s="5">
+        <f t="shared" si="5"/>
+        <v>46265</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.41666666666674601</v>
+      </c>
+      <c r="D11" s="5" t="str">
+        <f t="shared" ref="D11" si="7">IF(
+ AND(
+  B11 &gt;= IF(
+         YEAR(B11)&gt;=2007,
+         DATE(YEAR(B11),3,14)-WEEKDAY(DATE(YEAR(B11),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B11),4,7)-WEEKDAY(DATE(YEAR(B11),4,7),1)+1 + TIME(2,0,0)
+       ),
+  B11 &lt;  IF(
+         YEAR(B11)&gt;=2007,
+         DATE(YEAR(B11),11,7)-WEEKDAY(DATE(YEAR(B11),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B11),10,31)-WEEKDAY(DATE(YEAR(B11),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
       </c>
     </row>
   </sheetData>
